--- a/public/rl1.xlsx
+++ b/public/rl1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>АО "СТОКМАНН"</t>
   </si>
@@ -179,7 +179,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -395,11 +395,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -433,9 +496,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -519,6 +579,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -804,7 +885,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -818,114 +899,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:13" s="3" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:13" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
     </row>
     <row r="6" spans="1:13" s="5" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="43" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45" t="s">
+      <c r="F6" s="43"/>
+      <c r="G6" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="46"/>
+      <c r="H6" s="45"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="31"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="30"/>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="33" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -962,15 +1043,15 @@
       <c r="A12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="21" t="s">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="21" t="s">
         <v>27</v>
       </c>
     </row>
@@ -978,64 +1059,47 @@
       <c r="A13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="24"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="13" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="14"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="25"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="24"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:13" s="3" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:13" s="3" customFormat="1" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="15" t="s">
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="25"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="52"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:13" s="3" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="21"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="25"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/public/rl1.xlsx
+++ b/public/rl1.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Лист 1" sheetId="19" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="autoNoTable" iterateCount="1000" iterateDelta="9.9999999999999995E-8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -84,9 +84,6 @@
     <t>transpor + truckNumber</t>
   </si>
   <si>
-    <t>transportCompany</t>
-  </si>
-  <si>
     <t>MR №</t>
   </si>
   <si>
@@ -103,13 +100,16 @@
   </si>
   <si>
     <t>specialist</t>
+  </si>
+  <si>
+    <t>Общество с ограниченной ответственностью "УСПЕХ", 121596, Москва г, Горбунова ул, дом № 2, строение 3, помещение II, комната 12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +170,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -545,6 +553,27 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -575,31 +604,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -913,16 +921,16 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="A2" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -941,10 +949,10 @@
       <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="39"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="30"/>
       <c r="E4" s="31"/>
       <c r="F4" s="30"/>
@@ -965,19 +973,19 @@
       <c r="A6" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="41"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="32"/>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="45"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="52"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -994,14 +1002,14 @@
       <c r="A8" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="36"/>
+      <c r="B8" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
       <c r="H8" s="30"/>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1049,10 +1057,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
       <c r="G12" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="21" t="s">
         <v>26</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1065,7 +1073,7 @@
       <c r="C13" s="20"/>
       <c r="D13" s="23"/>
       <c r="E13" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="20"/>
@@ -1073,25 +1081,25 @@
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="51"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="52"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="39"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
